--- a/data/filtered/china_western.xlsx
+++ b/data/filtered/china_western.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2010-12-16</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3742360/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2013-12-03</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3804891/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>1995-04-12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293867/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>1986-01-30</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300508/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>1997-02-01</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1292843/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35206383/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>2000-05-26</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1297866/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2010-10-28</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4082544/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>2018-09-11</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30327768/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2010-06-22</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4078562/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2012-04-23</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10508901/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26200214/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2019-10-30</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30234426/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2017-12-12</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27063332/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35027217/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26812861/</t>
         </is>
